--- a/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
+++ b/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,10 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,6 +512,26 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Notes / good essay example?</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Year 年 (e.g. 833, 833?, 831-833)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Bai's place 白居易所在</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Addressee's post 受詩者官職</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Addressee's place 受詩者所在</t>
         </is>
       </c>
     </row>

--- a/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
+++ b/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
@@ -549,20 +549,64 @@
           <t>元九</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>元稹</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>元稹</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>史料一記元稹與白居易交好，江州、通州期間詩歌往還；這是白居易對元九的常見稱呼。</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>卷一·34</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>元稹</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>江陵府士曹參軍</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>江陵</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -578,20 +622,64 @@
           <t>劉二十八</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>劉禹錫</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>劉禹錫</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>全詩稱「夢得」；劉禹錫字夢得，亦見史料三。</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>卷三十·2011</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>劉禹錫</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>汝州刺史</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>汝州</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -607,20 +695,59 @@
           <t>李二十</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>已有知識：李紳行二十，曾任侍郎；史料三記他與白居易有詩文往來。</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>卷三十一·2055</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>太子賓客分司東都</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -636,20 +763,64 @@
           <t>李二十</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>已有知識：李紳行二十，曾赴浙東任職；詩題的官職和去處與之相合。</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>卷三十一·2068</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>浙東觀察使（檢校左散騎常侍、越州刺史）</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>越州</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -665,20 +836,54 @@
           <t>張十八</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>張籍</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>張籍</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>已有知識：張籍行十八，與韓愈交好；全詩稱他所游「獨言韓舍人」。</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>卷六·363</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>張籍</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -694,20 +899,59 @@
           <t>皇甫十</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>皇甫湜</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>皇甫曙</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>已有知識：皇甫曙行十；史料三記他與白居易有詩文往來。</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>卷三十二·2137</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>皇甫曙</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>郎中</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -723,20 +967,60 @@
           <t>楊六</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>楊汝士</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>詩題及全詩不足以確定此楊六的姓名。</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>卷三十二·2162</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>楊汝士</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>戶部侍郎</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -752,20 +1036,64 @@
           <t>楊六</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>楊汝士</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>楊虞卿</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>詩題稱其弟為漢公、魯士；已有知識及史料三所列楊氏人物可與楊虞卿相合。</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>卷三十四·2287</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>楊汝士</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>劍南東川節度使（檢校禮部尚書）</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>梓州</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -781,20 +1109,56 @@
           <t>楊八</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>詩題的官職和赴任地點不足以確定姓名。</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>卷三十一·2067</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>楊虞卿</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>給事中 → 常州刺史</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>常州</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -810,20 +1174,50 @@
           <t>崔十八</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>崔玄亮</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>詩題和全詩不足以確定這位崔十八的姓名。</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>外集卷上·3814</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>（箋校未注受贈人）</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -839,20 +1233,64 @@
           <t>牛二</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>牛僧孺</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>牛僧孺</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>已有知識：牛僧孺行二；史料一、三均記他與白居易有交往。</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>卷十七·1111</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>牛僧孺</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>考功員外郎</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -868,20 +1306,60 @@
           <t>李七</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>李宗閔</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>已有知識及詩題所示的員外郎身分可供推測；史料三記李宗閔與白居易有詩文往來。</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>卷十七·1112</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>李宗閔</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>員外郎（箋：或即吏部員外郎）</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -897,20 +1375,64 @@
           <t>庾三十二</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>庾承宣</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>庾敬休</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>史料三記庾敬休是白居易的朋友；據已有知識推測為詩題中的庾三十二。</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>卷十七·1113；卷十六·972</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>庾敬休</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>禮部員外郎</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -926,20 +1448,60 @@
           <t>崔二十二</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>崔羣</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>已有知識：崔羣行二十二，曾任果州刺史；史料一記他與白居易同在翰林。</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>卷十六·971</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>崔韶</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>果州刺史</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>果州</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -955,20 +1517,60 @@
           <t>韋大</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>韋處厚</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>已有知識：韋處厚曾在開州任職；史料三記白居易為他作祭文，並有詩文往來。</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>卷十六·971</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>韋處厚</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>開州刺史</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>開州</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -984,20 +1586,64 @@
           <t>杜十四</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>杜元穎</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>杜元穎</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>已有知識：杜元穎行十四；史料三記他是白居易的同年友。</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>卷十六·972</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>杜元穎</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>左拾遺</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1013,20 +1659,59 @@
           <t>竇七</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>竇鞏</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>竇鞏</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>已有知識：竇鞏行七；史料一記他與元稹酬唱，史料三記他與白居易有詩文往來。</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>卷十六·973</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>竇鞏</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>校書郎（箋：是時或已為校書）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1042,20 +1727,59 @@
           <t>李二十</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>已有知識：李紳行二十，曾任助教；史料一亦稱「李二十新歌行」。</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>卷十六·972</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>李紳</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>國子助教</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1071,20 +1795,59 @@
           <t>獨孤二十七</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>獨孤郁</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>獨孤郁</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>已有知識：獨孤郁行二十七，曾在翰林任職；史料三記其與白居易有詩文往來。</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>卷十四·805</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>獨孤郁</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>起居郎</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1100,20 +1863,59 @@
           <t>劉十九</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>劉禹銅</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>劉禹銅</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>已有知識中有將詩題的劉十九認作劉禹銅的說法；僅憑詩文本身不能確定。</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>卷十七·1072</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>嵩陽處士，名未詳（箋：非劉軻）</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>處士</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1129,20 +1931,59 @@
           <t>舒三</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>舒元輿</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>舒元輿</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>已有知識：舒元輿行三；史料三記其與白居易有詩文往來。</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>卷三十一·2049</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>舒元輿</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>員外郎（題稱）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1158,20 +1999,60 @@
           <t>嚴十八</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>嚴休復</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>已有知識：嚴休復曾在白居易之前任蘇州刺史；史料三記其與白居易有詩文往來。</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>卷八·456</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>嚴休復</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>郎中</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1187,20 +2068,55 @@
           <t>崔二十四</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>崔玄亮</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>已有知識：崔玄亮字晦叔，行二十四，曾任常侍；史料一亦記白居易與崔晦叔交往。</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>卷三十二·2122</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>崔咸</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>秘書監（右散騎常侍）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1216,20 +2132,55 @@
           <t>皇甫六</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>皇甫曙</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>詩題及全詩不足以確定這位皇甫六的姓名。</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>卷三十一·2060</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>皇甫鏞</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>太子賓客分司東都</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1245,20 +2196,59 @@
           <t>張十五</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>張仲素</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>張仲方</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>已有知識：張仲方行十五，曾為分司東都的賓客；史料三記他與白居易同僚並有詩文往來。</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>卷三十一·2060</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>張仲方</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>太子賓客分司東都</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1274,20 +2264,51 @@
           <t>李二十三</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>詩題及全詩不足以確定這位李二十三的姓名。</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>卷三十一·2060</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>李紳（箋作〔李二十賓客〕，題當讀「李二十／三賓客」）</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>太子賓客分司東都</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1303,20 +2324,46 @@
           <t>皇甫七</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>詩題和全詩不足以確定這位皇甫七的姓名。</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>卷二十三·1580</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>皇甫湜</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1332,20 +2379,54 @@
           <t>吳七</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>吳武陵</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>吳丹</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>已有知識：吳丹與白居易同年登進士第；全詩末句稱「進士有同年」，史料三亦記兩人交往。</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>卷六·368</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>吳丹</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1361,20 +2442,59 @@
           <t>沈四</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>沈傳師</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>沈述師</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>據已有知識推測沈四著作為沈述師；史料三記他與白居易有詩文往來。</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>卷三十三·2227</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>沈述師（箋疑「四」為「十四」之奪文）</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>著作郎</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1390,20 +2510,56 @@
           <t>劉五</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>詩題及全詩的官職、年齡線索不足以確定姓名。</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>卷三十一·2104</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>名未詳</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>峽州司馬</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>峽州</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1419,20 +2575,51 @@
           <t>韋七</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>詩題及全詩不足以確定這位韋七的姓名。</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>卷三十·2010</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>韋縝</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>太子庶子</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1448,20 +2635,51 @@
           <t>李六</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>全詩稱三人是同年，但不足以確定李六的姓名。</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>卷三十三·2187</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>白居易同年，名未出（箋：與江州途中詩之李六郎中非一人）</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>郎中</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1477,20 +2695,64 @@
           <t>楊十二</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>楊巨源</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>楊巨源</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>已有知識：楊巨源行十二，曾任國子博士；史料三記其收到白居易詩文。</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>卷十七·1102</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>楊巨源</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>江州</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>太常博士</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>長安</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1506,20 +2768,56 @@
           <t>李十九</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>詩題及全詩的蘄春任職和年齡線索不足以確定姓名。</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>卷三十四·2268</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>李播</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>洛陽</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>蘄州刺史</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>蘄州</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1535,20 +2833,51 @@
           <t>王十八</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>不知</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>詩題和全詩不足以確定這位王十八的姓名。</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>卷十三·759</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>王質夫</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>盩厔</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>處士</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
+++ b/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
@@ -584,8 +584,16 @@
           <t>元稹</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
@@ -657,8 +665,16 @@
           <t>劉禹錫</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -730,8 +746,16 @@
           <t>李紳</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -798,8 +822,16 @@
           <t>李紳</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -871,8 +903,16 @@
           <t>張籍</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
@@ -934,8 +974,16 @@
           <t>皇甫曙</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -998,8 +1046,16 @@
           <t>楊汝士</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
@@ -1071,8 +1127,16 @@
           <t>楊汝士</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1136,8 +1200,16 @@
           <t>楊虞卿</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
@@ -1205,8 +1277,16 @@
           <t>（箋校未注受贈人）</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -1268,8 +1348,16 @@
           <t>牛僧孺</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1337,8 +1425,16 @@
           <t>李宗閔</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1410,8 +1506,16 @@
           <t>庾敬休</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -1479,8 +1583,16 @@
           <t>崔韶</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
@@ -1548,8 +1660,16 @@
           <t>韋處厚</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
@@ -1621,8 +1741,16 @@
           <t>杜元穎</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -1694,8 +1822,16 @@
           <t>竇鞏</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
@@ -1762,8 +1898,16 @@
           <t>李紳</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
@@ -1830,8 +1974,16 @@
           <t>獨孤郁</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
@@ -1898,8 +2050,16 @@
           <t>嵩陽處士，名未詳（箋：非劉軻）</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -1966,8 +2126,16 @@
           <t>舒元輿</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
@@ -2030,8 +2198,16 @@
           <t>嚴休復</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
@@ -2099,8 +2275,16 @@
           <t>崔咸</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
@@ -2163,8 +2347,16 @@
           <t>皇甫鏞</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
@@ -2231,8 +2423,16 @@
           <t>張仲方</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
@@ -2291,8 +2491,16 @@
           <t>李紳（箋作〔李二十賓客〕，題當讀「李二十／三賓客」）</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
@@ -2351,8 +2559,16 @@
           <t>皇甫湜</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
@@ -2414,8 +2630,16 @@
           <t>吳丹</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
@@ -2477,8 +2701,16 @@
           <t>沈述師（箋疑「四」為「十四」之奪文）</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
@@ -2537,8 +2769,16 @@
           <t>名未詳</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
@@ -2602,8 +2842,16 @@
           <t>韋縝</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
@@ -2662,8 +2910,16 @@
           <t>白居易同年，名未出（箋：與江州途中詩之李六郎中非一人）</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
@@ -2730,8 +2986,16 @@
           <t>楊巨源</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
@@ -2795,8 +3059,16 @@
           <t>李播</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
@@ -2860,8 +3132,16 @@
           <t>王質夫</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
@@ -2931,11 +3211,11 @@
       </c>
       <c r="B2">
         <f>COUNTIF(Record!K2:K36,"correct")</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="C2">
         <f>COUNTIF(Record!L2:L36,"correct")</f>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2946,11 +3226,11 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Record!K2:K36,"wrong")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C3">
         <f>COUNTIF(Record!L2:L36,"wrong")</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2961,11 +3241,11 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Record!K2:K36,"declined: answer exists")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C4">
         <f>COUNTIF(Record!L2:L36,"declined: answer exists")</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2976,11 +3256,11 @@
       </c>
       <c r="B5">
         <f>COUNTIF(Record!K2:K36,"declined: none exists")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C5">
         <f>COUNTIF(Record!L2:L36,"declined: none exists")</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2991,11 +3271,11 @@
       </c>
       <c r="B6">
         <f>COUNTIF(Record!K2:K36,"partly")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C6">
         <f>COUNTIF(Record!L2:L36,"partly")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3006,11 +3286,11 @@
       </c>
       <c r="B7">
         <f>COUNTA(Record!K2:K36)</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="C7">
         <f>COUNTA(Record!L2:L36)</f>
-        <v/>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
+++ b/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,7 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,6 +535,16 @@
           <t>Addressee's place 受詩者所在</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>A evidence status (vs 箋校)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>B evidence status (vs 箋校)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -615,6 +626,16 @@
           <t>江陵</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -696,6 +717,16 @@
           <t>汝州</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -772,6 +803,16 @@
           <t>太子賓客分司東都</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -853,6 +894,16 @@
           <t>越州</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -924,6 +975,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1000,6 +1061,16 @@
           <t>郎中</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1077,6 +1148,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1158,6 +1239,16 @@
           <t>梓州</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1231,6 +1322,16 @@
           <t>常州</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1298,6 +1399,16 @@
           <t>洛陽</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>unverifiable: not annotated</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1379,6 +1490,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1456,6 +1577,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1537,6 +1668,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1614,6 +1755,16 @@
           <t>果州</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1691,6 +1842,16 @@
           <t>開州</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1772,6 +1933,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1848,6 +2019,16 @@
           <t>校書郎（箋：是時或已為校書）</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1924,6 +2105,16 @@
           <t>國子助教</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2000,6 +2191,16 @@
           <t>起居郎</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2076,6 +2277,16 @@
           <t>處士</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>unverifiable: name unknown</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>unverifiable: name unknown</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2152,6 +2363,16 @@
           <t>員外郎（題稱）</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2229,6 +2450,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2301,6 +2532,16 @@
           <t>秘書監（右散騎常侍）</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2373,6 +2614,16 @@
           <t>太子賓客分司東都</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2449,6 +2700,16 @@
           <t>太子賓客分司東都</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2517,6 +2778,16 @@
           <t>太子賓客分司東都</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2580,6 +2851,16 @@
           <t>洛陽</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2651,6 +2932,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2727,6 +3018,16 @@
           <t>著作郎</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2800,6 +3101,16 @@
           <t>峽州</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2868,6 +3179,16 @@
           <t>太子庶子</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2936,6 +3257,16 @@
           <t>郎中</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3017,6 +3348,16 @@
           <t>長安</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3090,6 +3431,16 @@
           <t>蘄州</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3158,14 +3509,27 @@
           <t>處士</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="K2:L36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"correct,wrong,declined: answer exists,declined: none exists,partly"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E36 G2:G36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"high,medium,low"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:S36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"matches reference,differs from reference,rejected by reference,unverifiable: not annotated,unverifiable: name unknown,declined: answer exists,declined: none exists"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3178,7 +3542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3293,6 +3657,150 @@
         <v>35</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Evidence status (Record R, S)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Condition A (title only)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Condition B (title + sources)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>matches reference</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>COUNTIF(Record!R2:R36,"matches reference")</f>
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <f>COUNTIF(Record!S2:S36,"matches reference")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>differs from reference</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>COUNTIF(Record!R2:R36,"differs from reference")</f>
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <f>COUNTIF(Record!S2:S36,"differs from reference")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rejected by reference</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>COUNTIF(Record!R2:R36,"rejected by reference")</f>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f>COUNTIF(Record!S2:S36,"rejected by reference")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>unverifiable: not annotated</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>COUNTIF(Record!R2:R36,"unverifiable: not annotated")</f>
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(Record!S2:S36,"unverifiable: not annotated")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>unverifiable: name unknown</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>COUNTIF(Record!R2:R36,"unverifiable: name unknown")</f>
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(Record!S2:S36,"unverifiable: name unknown")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>declined: answer exists</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>COUNTIF(Record!R2:R36,"declined: answer exists")</f>
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(Record!S2:S36,"declined: answer exists")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>declined: none exists</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>COUNTIF(Record!R2:R36,"declined: none exists")</f>
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(Record!S2:S36,"declined: none exists")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>total (evidence status)</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>COUNTA(Record!R2:R36)</f>
+        <v>35</v>
+      </c>
+      <c r="C17">
+        <f>COUNTA(Record!S2:S36)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Rows 2-7 keep the original rule: any name 箋校 does not give counts as wrong. Rows 10-17 split those answers by what 箋校 says; nothing is re-judged.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
+++ b/public/data/Bai-Juyi-Experiment-Record-Sheet.xlsx
@@ -2762,7 +2762,11 @@
           <t>declined: answer exists</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Student check (30 Oct 2026): 箋校 reads the title as 李二十／三賓客, so the form of address given to the AI, 李二十三, was itself a misreading. The verdict follows the rule (箋校 names 李紳), but this miss is partly the test's fault.</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>833</t>
@@ -2989,7 +2993,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>沈述師（箋疑「四」為「十四」之奪文）</t>
+          <t>沈述師（箋引岑仲勉《唐人行第錄》，謂「四」係「十四」之奪文，從之）</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3002,7 +3006,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Student check (30 Oct 2026): the 「十四」 reading is Cen Zhongmian's, which 箋校 accepts (其說是也); column J corrected.</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>837</t>
